--- a/Sedes_a_priorizar_Yanacona_2.xlsx
+++ b/Sedes_a_priorizar_Yanacona_2.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>51.27579827586207</v>
+        <v>53.02481577586207</v>
       </c>
     </row>
     <row r="3">
@@ -506,11 +506,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>219100000662</v>
+        <v>219022000189</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CENTRO EDUCATIVO PLACETILLAS</t>
+          <t>ESCUELA RURAL MIXTA DOMINGUILLO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -520,16 +520,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SAN JUAN</t>
+          <t>CAQUIONA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BOLIVAR</t>
+          <t>ALMAGUER</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>57.81541853448275</v>
+        <v>57.41377215517241</v>
       </c>
     </row>
     <row r="5">
@@ -562,11 +562,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>219392000552</v>
+        <v>219100000930</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CENTRO DOCENTE SANTA MARTA</t>
+          <t>ESCUELA RURAL MIXTA CIMARRONAS NUEVA GRANADA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -576,16 +576,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EL MORAL</t>
+          <t>SAN JUAN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LA SIERRA</t>
+          <t>BOLIVAR</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>59.70350818965517</v>
+        <v>59.31590853448276</v>
       </c>
     </row>
     <row r="7">
